--- a/product_upload/packages/15/file.xlsx
+++ b/product_upload/packages/15/file.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT101"/>
+  <dimension ref="A1:AU101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -600,7 +600,7 @@
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>Manufacture Name</t>
+          <t>Manufacturer Name</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
@@ -649,6 +649,11 @@
         </is>
       </c>
       <c r="AT1" t="inlineStr">
+        <is>
+          <t>Name / En</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
         <is>
           <t>Seller SKU</t>
         </is>
@@ -673,7 +678,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -836,6 +841,11 @@
       <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="inlineStr">
         <is>
+          <t>DEXTROSE 5% IN 0.45% SOD. CHLORIDE INF</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
           <t>SKU-D98E577EABE2</t>
         </is>
       </c>
@@ -859,7 +869,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1026,6 +1036,11 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
+          <t>DEXTROSE 5% IN 0.225% SOD. CHLORIDE INF</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
           <t>SKU-BA32C31983E6</t>
         </is>
       </c>
@@ -1049,7 +1064,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1216,6 +1231,11 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
+          <t>DEXTROSE 5% IN 0.225% SOD. CHLORIDE INF</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
           <t>SKU-DD0E5FF05479</t>
         </is>
       </c>
@@ -1239,7 +1259,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1398,6 +1418,11 @@
       <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="inlineStr">
         <is>
+          <t>DEXTROSE 5% IN 0.225% SOD. CHLORIDE INF</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
           <t>SKU-EDFE569F0294</t>
         </is>
       </c>
@@ -1421,7 +1446,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Kuwait</t>
+          <t>KW</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1576,6 +1601,11 @@
       <c r="AS6" t="inlineStr"/>
       <c r="AT6" t="inlineStr">
         <is>
+          <t>DEXTROSE 5% I.V INFUSION</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
           <t>SKU-82B398788EAD</t>
         </is>
       </c>
@@ -1599,7 +1629,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1762,6 +1792,11 @@
       <c r="AS7" t="inlineStr"/>
       <c r="AT7" t="inlineStr">
         <is>
+          <t>DEXTROSE 5% + 0.9% SODIUM CHLORIDE INFUSION</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
           <t>SKU-B534608ECE56</t>
         </is>
       </c>
@@ -1785,7 +1820,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1948,6 +1983,11 @@
       <c r="AS8" t="inlineStr"/>
       <c r="AT8" t="inlineStr">
         <is>
+          <t>DEXTROSE 5% + 0.9% SODIUM CHLORIDE INFUSION</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
           <t>SKU-820AE648E5A9</t>
         </is>
       </c>
@@ -1971,7 +2011,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -2134,6 +2174,11 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
+          <t>DEXTROSE 5% &amp; RINGER LACTATE INFUSION SOLUTION</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
           <t>SKU-FE0DDD6E7FB0</t>
         </is>
       </c>
@@ -2157,7 +2202,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -2320,6 +2365,11 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
+          <t>DEXTROSE 5%</t>
+        </is>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
           <t>SKU-1B6A979B4D77</t>
         </is>
       </c>
@@ -2343,7 +2393,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -2506,6 +2556,11 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
+          <t>DEXTROSE 5%</t>
+        </is>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
           <t>SKU-EC2273A83A71</t>
         </is>
       </c>
@@ -2529,7 +2584,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -2688,6 +2743,11 @@
       <c r="AS12" t="inlineStr"/>
       <c r="AT12" t="inlineStr">
         <is>
+          <t>DEXTROSE 5%</t>
+        </is>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
           <t>SKU-A3813341E7F7</t>
         </is>
       </c>
@@ -2711,7 +2771,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -2870,6 +2930,11 @@
       <c r="AS13" t="inlineStr"/>
       <c r="AT13" t="inlineStr">
         <is>
+          <t>DEXTROSE 5% IN RINGER SOLUTION</t>
+        </is>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
           <t>SKU-248B77CEB4D8</t>
         </is>
       </c>
@@ -2893,7 +2958,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -3056,6 +3121,11 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
+          <t>DEXTROSE 5% INFUSION</t>
+        </is>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
           <t>SKU-C46D6BDC6A76</t>
         </is>
       </c>
@@ -3079,7 +3149,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -3242,6 +3312,11 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
+          <t>DEXTROSE 5%</t>
+        </is>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
           <t>SKU-B81C7A136CFF</t>
         </is>
       </c>
@@ -3265,7 +3340,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -3428,6 +3503,11 @@
       <c r="AS16" t="inlineStr"/>
       <c r="AT16" t="inlineStr">
         <is>
+          <t>DEXTROSE 10%+N.SALINE INJ</t>
+        </is>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
           <t>SKU-502C0012B874</t>
         </is>
       </c>
@@ -3451,7 +3531,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -3610,6 +3690,11 @@
       <c r="AS17" t="inlineStr"/>
       <c r="AT17" t="inlineStr">
         <is>
+          <t>DEXTROSE 5%</t>
+        </is>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
           <t>SKU-9DBE7DEB719D</t>
         </is>
       </c>
@@ -3633,7 +3718,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -3788,6 +3873,11 @@
       <c r="AS18" t="inlineStr"/>
       <c r="AT18" t="inlineStr">
         <is>
+          <t>DEXTROSE 5%</t>
+        </is>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
           <t>SKU-F8ACE6C2B98B</t>
         </is>
       </c>
@@ -3811,7 +3901,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -3970,6 +4060,11 @@
       <c r="AS19" t="inlineStr"/>
       <c r="AT19" t="inlineStr">
         <is>
+          <t>DEXTROSE 40%</t>
+        </is>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
           <t>SKU-25A9E87AB8AA</t>
         </is>
       </c>
@@ -3993,7 +4088,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -4160,6 +4255,11 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
+          <t>DEXTROSE 4.3%IN 0.18%SOD.CHLORIDE INFU</t>
+        </is>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
           <t>SKU-F4D8CFB646F2</t>
         </is>
       </c>
@@ -4183,7 +4283,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -4346,6 +4446,11 @@
       <c r="AS21" t="inlineStr"/>
       <c r="AT21" t="inlineStr">
         <is>
+          <t>DEXTROSE 4.3%IN 0.18%SOD.CHLORIDE INFU</t>
+        </is>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
           <t>SKU-CE32D2B392A9</t>
         </is>
       </c>
@@ -4369,7 +4474,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -4528,6 +4633,11 @@
       <c r="AS22" t="inlineStr"/>
       <c r="AT22" t="inlineStr">
         <is>
+          <t>DEXTROSE 25% INJ</t>
+        </is>
+      </c>
+      <c r="AU22" t="inlineStr">
+        <is>
           <t>SKU-143B35048BF2</t>
         </is>
       </c>
@@ -4551,7 +4661,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -4710,6 +4820,11 @@
       <c r="AS23" t="inlineStr"/>
       <c r="AT23" t="inlineStr">
         <is>
+          <t>DEXTROSE 25% INJ</t>
+        </is>
+      </c>
+      <c r="AU23" t="inlineStr">
+        <is>
           <t>SKU-133BBB48F05E</t>
         </is>
       </c>
@@ -4733,7 +4848,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -4888,6 +5003,11 @@
       <c r="AS24" t="inlineStr"/>
       <c r="AT24" t="inlineStr">
         <is>
+          <t>DEXTROSE 25% INJ</t>
+        </is>
+      </c>
+      <c r="AU24" t="inlineStr">
+        <is>
           <t>SKU-390E1FD1E895</t>
         </is>
       </c>
@@ -4911,7 +5031,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -5074,6 +5194,11 @@
       </c>
       <c r="AT25" t="inlineStr">
         <is>
+          <t>DEXTROSE 25% INJ</t>
+        </is>
+      </c>
+      <c r="AU25" t="inlineStr">
+        <is>
           <t>SKU-3A53B107F8F1</t>
         </is>
       </c>
@@ -5097,7 +5222,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -5260,6 +5385,11 @@
       </c>
       <c r="AT26" t="inlineStr">
         <is>
+          <t>DEXTROSE 25% INJ</t>
+        </is>
+      </c>
+      <c r="AU26" t="inlineStr">
+        <is>
           <t>SKU-CD206EA61738</t>
         </is>
       </c>
@@ -5283,7 +5413,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -5442,6 +5572,11 @@
       <c r="AS27" t="inlineStr"/>
       <c r="AT27" t="inlineStr">
         <is>
+          <t>DEXTROSE 20% W-V INFUSION</t>
+        </is>
+      </c>
+      <c r="AU27" t="inlineStr">
+        <is>
           <t>SKU-61586D75E9D6</t>
         </is>
       </c>
@@ -5465,7 +5600,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -5620,6 +5755,11 @@
       <c r="AS28" t="inlineStr"/>
       <c r="AT28" t="inlineStr">
         <is>
+          <t>DEXTROSE 20% W-V INFUSION</t>
+        </is>
+      </c>
+      <c r="AU28" t="inlineStr">
+        <is>
           <t>SKU-466AED479EF8</t>
         </is>
       </c>
@@ -5643,7 +5783,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -5806,6 +5946,11 @@
       </c>
       <c r="AT29" t="inlineStr">
         <is>
+          <t>DEXTROSE 20% INJ</t>
+        </is>
+      </c>
+      <c r="AU29" t="inlineStr">
+        <is>
           <t>SKU-2E41F0B6B0D3</t>
         </is>
       </c>
@@ -5829,7 +5974,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -5992,6 +6137,11 @@
       </c>
       <c r="AT30" t="inlineStr">
         <is>
+          <t>DEXTROSE 20% INJ</t>
+        </is>
+      </c>
+      <c r="AU30" t="inlineStr">
+        <is>
           <t>SKU-4A07070C9877</t>
         </is>
       </c>
@@ -6015,7 +6165,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -6174,6 +6324,11 @@
       <c r="AS31" t="inlineStr"/>
       <c r="AT31" t="inlineStr">
         <is>
+          <t>20%W/V DEXTROSE injection, USP</t>
+        </is>
+      </c>
+      <c r="AU31" t="inlineStr">
+        <is>
           <t>SKU-066653D9C0AD</t>
         </is>
       </c>
@@ -6197,7 +6352,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -6360,6 +6515,11 @@
       </c>
       <c r="AT32" t="inlineStr">
         <is>
+          <t>DEXTROSE 20%</t>
+        </is>
+      </c>
+      <c r="AU32" t="inlineStr">
+        <is>
           <t>SKU-7934792FDAA2</t>
         </is>
       </c>
@@ -6383,7 +6543,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -6546,6 +6706,11 @@
       <c r="AS33" t="inlineStr"/>
       <c r="AT33" t="inlineStr">
         <is>
+          <t>DEXTROSE 2.5% IN 1-2 NORMAL SALINE</t>
+        </is>
+      </c>
+      <c r="AU33" t="inlineStr">
+        <is>
           <t>SKU-93C6F17B058E</t>
         </is>
       </c>
@@ -6569,7 +6734,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -6728,6 +6893,11 @@
       <c r="AS34" t="inlineStr"/>
       <c r="AT34" t="inlineStr">
         <is>
+          <t>DEXTROSE 40% INFUSION</t>
+        </is>
+      </c>
+      <c r="AU34" t="inlineStr">
+        <is>
           <t>SKU-E090932E2E16</t>
         </is>
       </c>
@@ -6751,7 +6921,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -6910,6 +7080,11 @@
       <c r="AS35" t="inlineStr"/>
       <c r="AT35" t="inlineStr">
         <is>
+          <t>DEXTROSE 40% INFUSION</t>
+        </is>
+      </c>
+      <c r="AU35" t="inlineStr">
+        <is>
           <t>SKU-252351C17EA0</t>
         </is>
       </c>
@@ -6933,7 +7108,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -7088,6 +7263,11 @@
       <c r="AS36" t="inlineStr"/>
       <c r="AT36" t="inlineStr">
         <is>
+          <t>DEXTROSE 40% INFUSION</t>
+        </is>
+      </c>
+      <c r="AU36" t="inlineStr">
+        <is>
           <t>SKU-6035E0B8F5B1</t>
         </is>
       </c>
@@ -7111,7 +7291,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -7270,6 +7450,11 @@
       <c r="AS37" t="inlineStr"/>
       <c r="AT37" t="inlineStr">
         <is>
+          <t>DEXTROSE 40% INFUSION</t>
+        </is>
+      </c>
+      <c r="AU37" t="inlineStr">
+        <is>
           <t>SKU-4F15EEA2479E</t>
         </is>
       </c>
@@ -7293,7 +7478,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -7448,6 +7633,11 @@
       <c r="AS38" t="inlineStr"/>
       <c r="AT38" t="inlineStr">
         <is>
+          <t>DEXTROSE 5%</t>
+        </is>
+      </c>
+      <c r="AU38" t="inlineStr">
+        <is>
           <t>SKU-0CB201673F9C</t>
         </is>
       </c>
@@ -7471,7 +7661,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -7634,6 +7824,11 @@
       </c>
       <c r="AT39" t="inlineStr">
         <is>
+          <t>DEXTROSE 5%</t>
+        </is>
+      </c>
+      <c r="AU39" t="inlineStr">
+        <is>
           <t>SKU-BD1A11CA242E</t>
         </is>
       </c>
@@ -7657,7 +7852,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -7812,6 +8007,11 @@
       <c r="AS40" t="inlineStr"/>
       <c r="AT40" t="inlineStr">
         <is>
+          <t>DEXTROSE 5%</t>
+        </is>
+      </c>
+      <c r="AU40" t="inlineStr">
+        <is>
           <t>SKU-C4A61EA6DF6C</t>
         </is>
       </c>
@@ -7835,7 +8035,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -7998,6 +8198,11 @@
       </c>
       <c r="AT41" t="inlineStr">
         <is>
+          <t>DEXTROSE 5%</t>
+        </is>
+      </c>
+      <c r="AU41" t="inlineStr">
+        <is>
           <t>SKU-02DB4D0B4950</t>
         </is>
       </c>
@@ -8021,7 +8226,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -8184,6 +8389,11 @@
       </c>
       <c r="AT42" t="inlineStr">
         <is>
+          <t>DEXTROSE 5%</t>
+        </is>
+      </c>
+      <c r="AU42" t="inlineStr">
+        <is>
           <t>SKU-D481D312221B</t>
         </is>
       </c>
@@ -8207,7 +8417,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -8362,6 +8572,11 @@
       <c r="AS43" t="inlineStr"/>
       <c r="AT43" t="inlineStr">
         <is>
+          <t>DEXTROSE 5%</t>
+        </is>
+      </c>
+      <c r="AU43" t="inlineStr">
+        <is>
           <t>SKU-C99F997DBD49</t>
         </is>
       </c>
@@ -8385,7 +8600,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -8552,6 +8767,11 @@
       <c r="AS44" t="inlineStr"/>
       <c r="AT44" t="inlineStr">
         <is>
+          <t>DEXTROSE 5%</t>
+        </is>
+      </c>
+      <c r="AU44" t="inlineStr">
+        <is>
           <t>SKU-EB7BC0D4D162</t>
         </is>
       </c>
@@ -8575,7 +8795,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -8734,6 +8954,11 @@
       <c r="AS45" t="inlineStr"/>
       <c r="AT45" t="inlineStr">
         <is>
+          <t>DEXTROSE 5%</t>
+        </is>
+      </c>
+      <c r="AU45" t="inlineStr">
+        <is>
           <t>SKU-F5F646ACD6F3</t>
         </is>
       </c>
@@ -8757,7 +8982,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -8920,6 +9145,11 @@
       </c>
       <c r="AT46" t="inlineStr">
         <is>
+          <t>DEXTROSE 5%</t>
+        </is>
+      </c>
+      <c r="AU46" t="inlineStr">
+        <is>
           <t>SKU-12F523996614</t>
         </is>
       </c>
@@ -8943,7 +9173,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -9106,6 +9336,11 @@
       </c>
       <c r="AT47" t="inlineStr">
         <is>
+          <t>DEXTROSE 5%</t>
+        </is>
+      </c>
+      <c r="AU47" t="inlineStr">
+        <is>
           <t>SKU-3928B7D48DC4</t>
         </is>
       </c>
@@ -9129,7 +9364,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -9292,6 +9527,11 @@
       </c>
       <c r="AT48" t="inlineStr">
         <is>
+          <t>DEXTROSE 5%</t>
+        </is>
+      </c>
+      <c r="AU48" t="inlineStr">
+        <is>
           <t>SKU-B3BEE19320D7</t>
         </is>
       </c>
@@ -9315,7 +9555,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -9474,6 +9714,11 @@
       <c r="AS49" t="inlineStr"/>
       <c r="AT49" t="inlineStr">
         <is>
+          <t>DEXTROSE 5%</t>
+        </is>
+      </c>
+      <c r="AU49" t="inlineStr">
+        <is>
           <t>SKU-C2CDC6E5EF25</t>
         </is>
       </c>
@@ -9497,7 +9742,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -9660,6 +9905,11 @@
       </c>
       <c r="AT50" t="inlineStr">
         <is>
+          <t>DEXTROSE 5%</t>
+        </is>
+      </c>
+      <c r="AU50" t="inlineStr">
+        <is>
           <t>SKU-BA618A8BDEC1</t>
         </is>
       </c>
@@ -9683,7 +9933,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -9842,6 +10092,11 @@
       <c r="AS51" t="inlineStr"/>
       <c r="AT51" t="inlineStr">
         <is>
+          <t>40% w/v DEXTROSE Injection USP</t>
+        </is>
+      </c>
+      <c r="AU51" t="inlineStr">
+        <is>
           <t>SKU-C2FE8FA26686</t>
         </is>
       </c>
@@ -9865,7 +10120,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -10020,6 +10275,11 @@
       <c r="AS52" t="inlineStr"/>
       <c r="AT52" t="inlineStr">
         <is>
+          <t>DEXTROSE 5%</t>
+        </is>
+      </c>
+      <c r="AU52" t="inlineStr">
+        <is>
           <t>SKU-3EC5196E37BF</t>
         </is>
       </c>
@@ -10043,7 +10303,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -10214,6 +10474,11 @@
       <c r="AS53" t="inlineStr"/>
       <c r="AT53" t="inlineStr">
         <is>
+          <t>DAKTACORT CREAM 20MG-GM</t>
+        </is>
+      </c>
+      <c r="AU53" t="inlineStr">
+        <is>
           <t>SKU-5B9E8F74A56C</t>
         </is>
       </c>
@@ -10237,7 +10502,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>DK</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -10404,6 +10669,11 @@
       <c r="AS54" t="inlineStr"/>
       <c r="AT54" t="inlineStr">
         <is>
+          <t>DAIVONEX OINT. 50MCG-G</t>
+        </is>
+      </c>
+      <c r="AU54" t="inlineStr">
+        <is>
           <t>SKU-ED4A6FED467D</t>
         </is>
       </c>
@@ -10427,7 +10697,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>DK</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -10598,6 +10868,11 @@
       </c>
       <c r="AT55" t="inlineStr">
         <is>
+          <t>DAIVONEX CREAM 50MCG-G</t>
+        </is>
+      </c>
+      <c r="AU55" t="inlineStr">
+        <is>
           <t>SKU-BF0491D4F8E8</t>
         </is>
       </c>
@@ -10621,7 +10896,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -10788,6 +11063,11 @@
       <c r="AS56" t="inlineStr"/>
       <c r="AT56" t="inlineStr">
         <is>
+          <t>DAIVOBET OINTMENT</t>
+        </is>
+      </c>
+      <c r="AU56" t="inlineStr">
+        <is>
           <t>SKU-F3F5CF07A51D</t>
         </is>
       </c>
@@ -10811,7 +11091,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -10978,6 +11258,11 @@
       <c r="AS57" t="inlineStr"/>
       <c r="AT57" t="inlineStr">
         <is>
+          <t>DAIVOBET GEL</t>
+        </is>
+      </c>
+      <c r="AU57" t="inlineStr">
+        <is>
           <t>SKU-E8952488C07E</t>
         </is>
       </c>
@@ -11001,7 +11286,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -11174,6 +11459,11 @@
       <c r="AS58" t="inlineStr"/>
       <c r="AT58" t="inlineStr">
         <is>
+          <t>DAFLON 500MG TAB</t>
+        </is>
+      </c>
+      <c r="AU58" t="inlineStr">
+        <is>
           <t>SKU-43A417B1F2B7</t>
         </is>
       </c>
@@ -11197,7 +11487,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -11364,6 +11654,11 @@
       <c r="AS59" t="inlineStr"/>
       <c r="AT59" t="inlineStr">
         <is>
+          <t>DAKTARIN CREAM 2%</t>
+        </is>
+      </c>
+      <c r="AU59" t="inlineStr">
+        <is>
           <t>SKU-1AF84053C176</t>
         </is>
       </c>
@@ -11387,7 +11682,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -11554,6 +11849,11 @@
       <c r="AS60" t="inlineStr"/>
       <c r="AT60" t="inlineStr">
         <is>
+          <t>DAKTARIN ORAL GEL 2%</t>
+        </is>
+      </c>
+      <c r="AU60" t="inlineStr">
+        <is>
           <t>SKU-F9E9FFE01C69</t>
         </is>
       </c>
@@ -11577,7 +11877,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -11736,6 +12036,11 @@
       <c r="AS61" t="inlineStr"/>
       <c r="AT61" t="inlineStr">
         <is>
+          <t>DAKTARIN POWDER 2%</t>
+        </is>
+      </c>
+      <c r="AU61" t="inlineStr">
+        <is>
           <t>SKU-94D2A042635B</t>
         </is>
       </c>
@@ -11759,7 +12064,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -11926,6 +12231,11 @@
       <c r="AS62" t="inlineStr"/>
       <c r="AT62" t="inlineStr">
         <is>
+          <t>DAROXIME</t>
+        </is>
+      </c>
+      <c r="AU62" t="inlineStr">
+        <is>
           <t>SKU-1D473C4B191D</t>
         </is>
       </c>
@@ -11949,7 +12259,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -12104,6 +12414,11 @@
       <c r="AS63" t="inlineStr"/>
       <c r="AT63" t="inlineStr">
         <is>
+          <t>DAROXIME 250 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU63" t="inlineStr">
+        <is>
           <t>SKU-83E086BFAC18</t>
         </is>
       </c>
@@ -12127,7 +12442,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -12294,6 +12609,11 @@
       <c r="AS64" t="inlineStr"/>
       <c r="AT64" t="inlineStr">
         <is>
+          <t>DAONIL M 500/5MG TABLETS</t>
+        </is>
+      </c>
+      <c r="AU64" t="inlineStr">
+        <is>
           <t>SKU-0DF8806A4CAD</t>
         </is>
       </c>
@@ -12317,7 +12637,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -12484,6 +12804,11 @@
       <c r="AS65" t="inlineStr"/>
       <c r="AT65" t="inlineStr">
         <is>
+          <t>DAONIL M 500/2.5MG TABLETS</t>
+        </is>
+      </c>
+      <c r="AU65" t="inlineStr">
+        <is>
           <t>SKU-57DAF10DD0FA</t>
         </is>
       </c>
@@ -12507,7 +12832,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -12666,6 +12991,11 @@
       <c r="AS66" t="inlineStr"/>
       <c r="AT66" t="inlineStr">
         <is>
+          <t>DAONIL M 250/1.25MG TABLETS</t>
+        </is>
+      </c>
+      <c r="AU66" t="inlineStr">
+        <is>
           <t>SKU-260065A5D6AB</t>
         </is>
       </c>
@@ -12689,7 +13019,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -12862,6 +13192,11 @@
       </c>
       <c r="AT67" t="inlineStr">
         <is>
+          <t>DAONIL 5MG TAB</t>
+        </is>
+      </c>
+      <c r="AU67" t="inlineStr">
+        <is>
           <t>SKU-3B17345D958B</t>
         </is>
       </c>
@@ -12885,7 +13220,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -13052,6 +13387,11 @@
       <c r="AS68" t="inlineStr"/>
       <c r="AT68" t="inlineStr">
         <is>
+          <t>DALACIN VAGINAL CREAM 2%</t>
+        </is>
+      </c>
+      <c r="AU68" t="inlineStr">
+        <is>
           <t>SKU-8EDCF393AAFF</t>
         </is>
       </c>
@@ -13075,7 +13415,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -13246,6 +13586,11 @@
       </c>
       <c r="AT69" t="inlineStr">
         <is>
+          <t>DALACIN T LOTION 1%</t>
+        </is>
+      </c>
+      <c r="AU69" t="inlineStr">
+        <is>
           <t>SKU-3075AD41BFE1</t>
         </is>
       </c>
@@ -13269,7 +13614,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -13432,6 +13777,11 @@
       <c r="AS70" t="inlineStr"/>
       <c r="AT70" t="inlineStr">
         <is>
+          <t>CURACNE 40MG SOFT GELATIN CAPSULE</t>
+        </is>
+      </c>
+      <c r="AU70" t="inlineStr">
+        <is>
           <t>SKU-68B8BC8DCAAB</t>
         </is>
       </c>
@@ -13455,7 +13805,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -13614,6 +13964,11 @@
       <c r="AS71" t="inlineStr"/>
       <c r="AT71" t="inlineStr">
         <is>
+          <t>CURACNE 20MG SOFT GELATIN CAPSULE</t>
+        </is>
+      </c>
+      <c r="AU71" t="inlineStr">
+        <is>
           <t>SKU-234AC1C27248</t>
         </is>
       </c>
@@ -13637,7 +13992,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -13800,6 +14155,11 @@
       </c>
       <c r="AT72" t="inlineStr">
         <is>
+          <t>CURACNE 10MG SOFT GELATIN CAPSULE</t>
+        </is>
+      </c>
+      <c r="AU72" t="inlineStr">
+        <is>
           <t>SKU-170BE96FEE00</t>
         </is>
       </c>
@@ -13823,7 +14183,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -13994,6 +14354,11 @@
       </c>
       <c r="AT73" t="inlineStr">
         <is>
+          <t>CUPIDO</t>
+        </is>
+      </c>
+      <c r="AU73" t="inlineStr">
+        <is>
           <t>SKU-1C74D553985B</t>
         </is>
       </c>
@@ -14017,7 +14382,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -14180,6 +14545,11 @@
       </c>
       <c r="AT74" t="inlineStr">
         <is>
+          <t>CROTAPHIL 10% LOTION</t>
+        </is>
+      </c>
+      <c r="AU74" t="inlineStr">
+        <is>
           <t>SKU-11B898D36E56</t>
         </is>
       </c>
@@ -14203,7 +14573,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -14362,6 +14732,11 @@
       <c r="AS75" t="inlineStr"/>
       <c r="AT75" t="inlineStr">
         <is>
+          <t>CROTAPHIL 10% CREAM</t>
+        </is>
+      </c>
+      <c r="AU75" t="inlineStr">
+        <is>
           <t>SKU-100A9E78F0F3</t>
         </is>
       </c>
@@ -14385,7 +14760,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -14552,6 +14927,11 @@
       <c r="AS76" t="inlineStr"/>
       <c r="AT76" t="inlineStr">
         <is>
+          <t>CROMA EYE DROP</t>
+        </is>
+      </c>
+      <c r="AU76" t="inlineStr">
+        <is>
           <t>SKU-84B8FBF5D75D</t>
         </is>
       </c>
@@ -14575,7 +14955,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -14748,6 +15128,11 @@
       </c>
       <c r="AT77" t="inlineStr">
         <is>
+          <t>CRESTOR 20 MG FILM COATED TABLETS</t>
+        </is>
+      </c>
+      <c r="AU77" t="inlineStr">
+        <is>
           <t>SKU-69BEEE402EAC</t>
         </is>
       </c>
@@ -14771,7 +15156,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -14940,6 +15325,11 @@
       <c r="AS78" t="inlineStr"/>
       <c r="AT78" t="inlineStr">
         <is>
+          <t>CRESTOR 10 MG FILM COATED TABLETS</t>
+        </is>
+      </c>
+      <c r="AU78" t="inlineStr">
+        <is>
           <t>SKU-198DB8DAC639</t>
         </is>
       </c>
@@ -14963,7 +15353,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -15132,6 +15522,11 @@
       <c r="AS79" t="inlineStr"/>
       <c r="AT79" t="inlineStr">
         <is>
+          <t>COZAAR 100 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU79" t="inlineStr">
+        <is>
           <t>SKU-7DB454E1D0F9</t>
         </is>
       </c>
@@ -15155,7 +15550,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -15324,6 +15719,11 @@
       <c r="AS80" t="inlineStr"/>
       <c r="AT80" t="inlineStr">
         <is>
+          <t>COZAAR</t>
+        </is>
+      </c>
+      <c r="AU80" t="inlineStr">
+        <is>
           <t>SKU-0B01120AAA01</t>
         </is>
       </c>
@@ -15347,7 +15747,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -15514,6 +15914,11 @@
       <c r="AS81" t="inlineStr"/>
       <c r="AT81" t="inlineStr">
         <is>
+          <t>COXICAM</t>
+        </is>
+      </c>
+      <c r="AU81" t="inlineStr">
+        <is>
           <t>SKU-7528CFE76EFF</t>
         </is>
       </c>
@@ -15537,7 +15942,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -15704,6 +16109,11 @@
       <c r="AS82" t="inlineStr"/>
       <c r="AT82" t="inlineStr">
         <is>
+          <t>COXICAM</t>
+        </is>
+      </c>
+      <c r="AU82" t="inlineStr">
+        <is>
           <t>SKU-316664E6AAEB</t>
         </is>
       </c>
@@ -15727,7 +16137,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -15894,6 +16304,11 @@
       <c r="AS83" t="inlineStr"/>
       <c r="AT83" t="inlineStr">
         <is>
+          <t>COXICAM</t>
+        </is>
+      </c>
+      <c r="AU83" t="inlineStr">
+        <is>
           <t>SKU-793979CC9817</t>
         </is>
       </c>
@@ -15917,7 +16332,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -16076,6 +16491,11 @@
       <c r="AS84" t="inlineStr"/>
       <c r="AT84" t="inlineStr">
         <is>
+          <t>CURAM 156.25MG-5ML POWDER FOR SUSP</t>
+        </is>
+      </c>
+      <c r="AU84" t="inlineStr">
+        <is>
           <t>SKU-E3F42104F0B7</t>
         </is>
       </c>
@@ -16099,7 +16519,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -16274,6 +16694,11 @@
       </c>
       <c r="AT85" t="inlineStr">
         <is>
+          <t>CURAM 1GM TABLET</t>
+        </is>
+      </c>
+      <c r="AU85" t="inlineStr">
+        <is>
           <t>SKU-EE7B51431046</t>
         </is>
       </c>
@@ -16297,7 +16722,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -16472,6 +16897,11 @@
       </c>
       <c r="AT86" t="inlineStr">
         <is>
+          <t>CURAM 312.5 MG-5ML POWDER FOR SUSP</t>
+        </is>
+      </c>
+      <c r="AU86" t="inlineStr">
+        <is>
           <t>SKU-B16171ACA76A</t>
         </is>
       </c>
@@ -16495,7 +16925,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Lebanon</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -16654,6 +17084,11 @@
       <c r="AS87" t="inlineStr"/>
       <c r="AT87" t="inlineStr">
         <is>
+          <t>C-VITAL 1G EFFERVESCENT TABLETS SUGAR FREE</t>
+        </is>
+      </c>
+      <c r="AU87" t="inlineStr">
+        <is>
           <t>SKU-A791367F258C</t>
         </is>
       </c>
@@ -16677,7 +17112,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -16840,6 +17275,11 @@
       </c>
       <c r="AT88" t="inlineStr">
         <is>
+          <t>CUTIVATE 0.005% ointment</t>
+        </is>
+      </c>
+      <c r="AU88" t="inlineStr">
+        <is>
           <t>SKU-8552384FE9F0</t>
         </is>
       </c>
@@ -16863,7 +17303,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -17034,6 +17474,11 @@
       <c r="AS89" t="inlineStr"/>
       <c r="AT89" t="inlineStr">
         <is>
+          <t>CURAM 625 MG F.C TAB</t>
+        </is>
+      </c>
+      <c r="AU89" t="inlineStr">
+        <is>
           <t>SKU-C0B61E30CA65</t>
         </is>
       </c>
@@ -17057,7 +17502,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -17220,6 +17665,11 @@
       <c r="AS90" t="inlineStr"/>
       <c r="AT90" t="inlineStr">
         <is>
+          <t>CURAM 457MG-5ML POW. FOR ORAL SUSPENSION</t>
+        </is>
+      </c>
+      <c r="AU90" t="inlineStr">
+        <is>
           <t>SKU-4FD6164089CE</t>
         </is>
       </c>
@@ -17243,7 +17693,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -17402,6 +17852,11 @@
       <c r="AS91" t="inlineStr"/>
       <c r="AT91" t="inlineStr">
         <is>
+          <t>CUTIVATE 0.05% cream</t>
+        </is>
+      </c>
+      <c r="AU91" t="inlineStr">
+        <is>
           <t>SKU-A4DA750E3163</t>
         </is>
       </c>
@@ -17425,7 +17880,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -17588,6 +18043,11 @@
       </c>
       <c r="AT92" t="inlineStr">
         <is>
+          <t>DERMOFUCIN 2% OINTMENT</t>
+        </is>
+      </c>
+      <c r="AU92" t="inlineStr">
+        <is>
           <t>SKU-E8C5530050C7</t>
         </is>
       </c>
@@ -17611,7 +18071,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -17782,6 +18242,11 @@
       </c>
       <c r="AT93" t="inlineStr">
         <is>
+          <t>DERMOFUCIN 2% CREAM</t>
+        </is>
+      </c>
+      <c r="AU93" t="inlineStr">
+        <is>
           <t>SKU-6CB7EFA6D6BE</t>
         </is>
       </c>
@@ -17805,7 +18270,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -17964,6 +18429,11 @@
       <c r="AS94" t="inlineStr"/>
       <c r="AT94" t="inlineStr">
         <is>
+          <t>DERMOFIX 2% CREAM</t>
+        </is>
+      </c>
+      <c r="AU94" t="inlineStr">
+        <is>
           <t>SKU-2445A14AE696</t>
         </is>
       </c>
@@ -17987,7 +18457,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -18142,6 +18612,11 @@
       <c r="AS95" t="inlineStr"/>
       <c r="AT95" t="inlineStr">
         <is>
+          <t>DERMOCORT CREAM</t>
+        </is>
+      </c>
+      <c r="AU95" t="inlineStr">
+        <is>
           <t>SKU-802850C2D806</t>
         </is>
       </c>
@@ -18165,7 +18640,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -18328,6 +18803,11 @@
       <c r="AS96" t="inlineStr"/>
       <c r="AT96" t="inlineStr">
         <is>
+          <t>DERMATIN SOLUTION 1%</t>
+        </is>
+      </c>
+      <c r="AU96" t="inlineStr">
+        <is>
           <t>SKU-D7D881AC6DF2</t>
         </is>
       </c>
@@ -18351,7 +18831,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -18514,6 +18994,11 @@
       </c>
       <c r="AT97" t="inlineStr">
         <is>
+          <t>DERMATIN CREAM 1%</t>
+        </is>
+      </c>
+      <c r="AU97" t="inlineStr">
+        <is>
           <t>SKU-4FF1ED655CD5</t>
         </is>
       </c>
@@ -18537,7 +19022,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -18708,6 +19193,11 @@
       </c>
       <c r="AT98" t="inlineStr">
         <is>
+          <t>DERMA-T SOLUTION</t>
+        </is>
+      </c>
+      <c r="AU98" t="inlineStr">
+        <is>
           <t>SKU-C72B2858340D</t>
         </is>
       </c>
@@ -18731,7 +19221,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -18890,6 +19380,11 @@
       <c r="AS99" t="inlineStr"/>
       <c r="AT99" t="inlineStr">
         <is>
+          <t>DERMAMED 0.05% OINTMENT</t>
+        </is>
+      </c>
+      <c r="AU99" t="inlineStr">
+        <is>
           <t>SKU-2C797AA5E4C5</t>
         </is>
       </c>
@@ -18913,7 +19408,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -19080,6 +19575,11 @@
       <c r="AS100" t="inlineStr"/>
       <c r="AT100" t="inlineStr">
         <is>
+          <t>DERMA T 10MG TOPICAL LOTION</t>
+        </is>
+      </c>
+      <c r="AU100" t="inlineStr">
+        <is>
           <t>SKU-DE340B06301F</t>
         </is>
       </c>
@@ -19103,7 +19603,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -19275,6 +19775,11 @@
         </is>
       </c>
       <c r="AT101" t="inlineStr">
+        <is>
+          <t>DERMOVATE 0.05% SCALP APPLICATION</t>
+        </is>
+      </c>
+      <c r="AU101" t="inlineStr">
         <is>
           <t>SKU-22C49EC8A89C</t>
         </is>
@@ -19291,7 +19796,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB13"/>
+  <dimension ref="A1:AC13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19337,100 +19842,105 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
+          <t>Manufacturer Name</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
           <t>Seller SKU</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Level 1*</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Level 2*</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Level 3*</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Risk Class *</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Sterility</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Brand</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Model / Catalogue Number</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Single Use</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Legal Manufacturer</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>UDI-DI</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>GMDN Code / Term</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>SFDA Authorized Representative License No.</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Size</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Power Source</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Warranty</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Storage Conditions / En</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Usage Instructions</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Branch id</t>
         </is>
@@ -19462,7 +19972,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -19477,92 +19987,97 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>SKU-60257</t>
         </is>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>469.75</v>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>Medical Devices</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Home Health Test</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T2" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U2" t="inlineStr">
+      <c r="U2" t="n">
+        <v>61</v>
+      </c>
+      <c r="V2" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W2" t="n">
+      <c r="X2" t="n">
         <v>100</v>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y2" t="n">
+      <c r="Z2" t="n">
         <v>12</v>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19594,7 +20109,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -19609,92 +20124,97 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>SKU-51001</t>
         </is>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>234.31</v>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Wheelchairs &amp; Scooters</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T3" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U3" t="inlineStr">
+      <c r="U3" t="n">
+        <v>62</v>
+      </c>
+      <c r="V3" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W3" t="n">
+      <c r="X3" t="n">
         <v>100</v>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y3" t="n">
+      <c r="Z3" t="n">
         <v>12</v>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19726,7 +20246,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -19741,92 +20261,97 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>SKU-17866</t>
         </is>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>204.09</v>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>Medical Devices</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>Diabetic Care</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T4" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U4" t="inlineStr">
+      <c r="U4" t="n">
+        <v>63</v>
+      </c>
+      <c r="V4" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W4" t="n">
+      <c r="X4" t="n">
         <v>100</v>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y4" t="n">
+      <c r="Z4" t="n">
         <v>12</v>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19858,7 +20383,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -19873,92 +20398,97 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>SKU-65211</t>
         </is>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>153.58</v>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>Medical Devices</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>Diabetic Care</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T5" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U5" t="inlineStr">
+      <c r="U5" t="n">
+        <v>64</v>
+      </c>
+      <c r="V5" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W5" t="n">
+      <c r="X5" t="n">
         <v>100</v>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y5" t="n">
+      <c r="Z5" t="n">
         <v>12</v>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19990,7 +20520,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -20005,92 +20535,97 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>SKU-78870</t>
         </is>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>191.8</v>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>Medical Devices</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>Diabetic Care</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T6" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U6" t="inlineStr">
+      <c r="U6" t="n">
+        <v>65</v>
+      </c>
+      <c r="V6" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W6" t="n">
+      <c r="X6" t="n">
         <v>100</v>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y6" t="n">
+      <c r="Z6" t="n">
         <v>12</v>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20122,7 +20657,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -20137,92 +20672,97 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>SKU-59373</t>
         </is>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
         <v>274.77</v>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>Medical Devices</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>Thermometer</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T7" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U7" t="inlineStr">
+      <c r="U7" t="n">
+        <v>66</v>
+      </c>
+      <c r="V7" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W7" t="n">
+      <c r="X7" t="n">
         <v>100</v>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y7" t="n">
+      <c r="Z7" t="n">
         <v>12</v>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20254,7 +20794,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -20269,92 +20809,97 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>SKU-83458</t>
         </is>
       </c>
-      <c r="J8" t="n">
+      <c r="K8" t="n">
         <v>232.33</v>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>Medical Devices</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>Diabetic Care</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T8" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U8" t="inlineStr">
+      <c r="U8" t="n">
+        <v>67</v>
+      </c>
+      <c r="V8" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W8" t="n">
+      <c r="X8" t="n">
         <v>100</v>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y8" t="n">
+      <c r="Z8" t="n">
         <v>12</v>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="AA8" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20386,7 +20931,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -20401,92 +20946,97 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>SKU-60955</t>
         </is>
       </c>
-      <c r="J9" t="n">
+      <c r="K9" t="n">
         <v>255.98</v>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T9" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U9" t="inlineStr">
+      <c r="U9" t="n">
+        <v>68</v>
+      </c>
+      <c r="V9" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W9" t="n">
+      <c r="X9" t="n">
         <v>100</v>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y9" t="n">
+      <c r="Z9" t="n">
         <v>12</v>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="AA9" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr">
+      <c r="AB9" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20518,7 +21068,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -20533,92 +21083,97 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>SKU-47960</t>
         </is>
       </c>
-      <c r="J10" t="n">
+      <c r="K10" t="n">
         <v>418.33</v>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T10" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U10" t="inlineStr">
+      <c r="U10" t="n">
+        <v>69</v>
+      </c>
+      <c r="V10" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W10" t="n">
+      <c r="X10" t="n">
         <v>100</v>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="Y10" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y10" t="n">
+      <c r="Z10" t="n">
         <v>12</v>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="AA10" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA10" t="inlineStr">
+      <c r="AB10" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AC10" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20650,7 +21205,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -20665,92 +21220,97 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
           <t>SKU-52207</t>
         </is>
       </c>
-      <c r="J11" t="n">
+      <c r="K11" t="n">
         <v>396.53</v>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T11" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U11" t="inlineStr">
+      <c r="U11" t="n">
+        <v>70</v>
+      </c>
+      <c r="V11" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W11" t="n">
+      <c r="X11" t="n">
         <v>100</v>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="Y11" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y11" t="n">
+      <c r="Z11" t="n">
         <v>12</v>
       </c>
-      <c r="Z11" t="inlineStr">
+      <c r="AA11" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA11" t="inlineStr">
+      <c r="AB11" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
+      <c r="AC11" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20782,7 +21342,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -20797,92 +21357,97 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
           <t>SKU-87461</t>
         </is>
       </c>
-      <c r="J12" t="n">
+      <c r="K12" t="n">
         <v>223.89</v>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T12" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U12" t="inlineStr">
+      <c r="U12" t="n">
+        <v>71</v>
+      </c>
+      <c r="V12" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W12" t="n">
+      <c r="X12" t="n">
         <v>100</v>
       </c>
-      <c r="X12" t="inlineStr">
+      <c r="Y12" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y12" t="n">
+      <c r="Z12" t="n">
         <v>12</v>
       </c>
-      <c r="Z12" t="inlineStr">
+      <c r="AA12" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA12" t="inlineStr">
+      <c r="AB12" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
+      <c r="AC12" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20914,7 +21479,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -20929,92 +21494,97 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
           <t>SKU-79669</t>
         </is>
       </c>
-      <c r="J13" t="n">
+      <c r="K13" t="n">
         <v>486.85</v>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>Medical Devices</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>Thermometer</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="P13" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
+      <c r="Q13" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr">
+      <c r="R13" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T13" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U13" t="inlineStr">
+      <c r="U13" t="n">
+        <v>72</v>
+      </c>
+      <c r="V13" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W13" t="n">
+      <c r="X13" t="n">
         <v>100</v>
       </c>
-      <c r="X13" t="inlineStr">
+      <c r="Y13" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y13" t="n">
+      <c r="Z13" t="n">
         <v>12</v>
       </c>
-      <c r="Z13" t="inlineStr">
+      <c r="AA13" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA13" t="inlineStr">
+      <c r="AB13" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
+      <c r="AC13" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -21031,7 +21601,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U21"/>
+  <dimension ref="A1:W21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21137,6 +21707,16 @@
       </c>
       <c r="U1" t="inlineStr">
         <is>
+          <t>Manufacturer Name</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>Ingredients</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>Seller SKU</t>
         </is>
       </c>
@@ -21172,7 +21752,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -21237,6 +21817,16 @@
         </is>
       </c>
       <c r="U2" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
         <is>
           <t>SKU-9F0B489DF7CC</t>
         </is>
@@ -21273,7 +21863,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -21338,6 +21928,16 @@
         </is>
       </c>
       <c r="U3" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
         <is>
           <t>SKU-84C48657A165</t>
         </is>
@@ -21374,7 +21974,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -21439,6 +22039,16 @@
         </is>
       </c>
       <c r="U4" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
         <is>
           <t>SKU-091651EA21BE</t>
         </is>
@@ -21475,7 +22085,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -21540,6 +22150,16 @@
         </is>
       </c>
       <c r="U5" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
         <is>
           <t>SKU-7348A57795DE</t>
         </is>
@@ -21576,7 +22196,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -21641,6 +22261,16 @@
         </is>
       </c>
       <c r="U6" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
         <is>
           <t>SKU-FBE99303C427</t>
         </is>
@@ -21677,7 +22307,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -21742,6 +22372,16 @@
         </is>
       </c>
       <c r="U7" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
         <is>
           <t>SKU-B3E73661A217</t>
         </is>
@@ -21778,7 +22418,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -21843,6 +22483,16 @@
         </is>
       </c>
       <c r="U8" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
         <is>
           <t>SKU-88453BC061E7</t>
         </is>
@@ -21879,7 +22529,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -21944,6 +22594,16 @@
         </is>
       </c>
       <c r="U9" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
         <is>
           <t>SKU-A3F87921111E</t>
         </is>
@@ -21980,7 +22640,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -22045,6 +22705,16 @@
         </is>
       </c>
       <c r="U10" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
         <is>
           <t>SKU-3CDB8300509A</t>
         </is>
@@ -22081,7 +22751,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -22146,6 +22816,16 @@
         </is>
       </c>
       <c r="U11" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
         <is>
           <t>SKU-8A85C717FFC7</t>
         </is>
@@ -22182,7 +22862,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -22247,6 +22927,16 @@
         </is>
       </c>
       <c r="U12" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
         <is>
           <t>SKU-81ABEA1344B7</t>
         </is>
@@ -22283,7 +22973,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -22348,6 +23038,16 @@
         </is>
       </c>
       <c r="U13" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
         <is>
           <t>SKU-0921B8871FEF</t>
         </is>
@@ -22384,7 +23084,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -22449,6 +23149,16 @@
         </is>
       </c>
       <c r="U14" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
         <is>
           <t>SKU-DAA2A726F88E</t>
         </is>
@@ -22485,7 +23195,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -22550,6 +23260,16 @@
         </is>
       </c>
       <c r="U15" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
         <is>
           <t>SKU-0427C106C43D</t>
         </is>
@@ -22586,7 +23306,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -22651,6 +23371,16 @@
         </is>
       </c>
       <c r="U16" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
         <is>
           <t>SKU-040E51D202AC</t>
         </is>
@@ -22687,7 +23417,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -22752,6 +23482,16 @@
         </is>
       </c>
       <c r="U17" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
         <is>
           <t>SKU-AE3B9F5DA6AE</t>
         </is>
@@ -22788,7 +23528,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -22853,6 +23593,16 @@
         </is>
       </c>
       <c r="U18" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
         <is>
           <t>SKU-3E23EDE5D020</t>
         </is>
@@ -22889,7 +23639,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -22954,6 +23704,16 @@
         </is>
       </c>
       <c r="U19" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
         <is>
           <t>SKU-34E3D0AB0069</t>
         </is>
@@ -22990,7 +23750,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -23055,6 +23815,16 @@
         </is>
       </c>
       <c r="U20" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
         <is>
           <t>SKU-9C169E05E23F</t>
         </is>
@@ -23091,7 +23861,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -23156,6 +23926,16 @@
         </is>
       </c>
       <c r="U21" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
         <is>
           <t>SKU-A33626DD6EE7</t>
         </is>

--- a/product_upload/packages/15/file.xlsx
+++ b/product_upload/packages/15/file.xlsx
@@ -686,8 +686,16 @@
           <t>1357016660-649-247456519807</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DEXTROSE 5% IN 0.45% SOD. CHLORIDE INF</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>DEXTROSE 5% IN 0.45% SOD. CHLORIDE INF detailed description.</t>
+        </is>
+      </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
@@ -877,8 +885,16 @@
           <t>5732549013-773-566130345672</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DEXTROSE 5% IN 0.225% SOD. CHLORIDE INF</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>DEXTROSE 5% IN 0.225% SOD. CHLORIDE INF detailed description.</t>
+        </is>
+      </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
@@ -1072,8 +1088,16 @@
           <t>4883730943-065-572206869172</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DEXTROSE 5% IN 0.225% SOD. CHLORIDE INF</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>DEXTROSE 5% IN 0.225% SOD. CHLORIDE INF detailed description.</t>
+        </is>
+      </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
@@ -1267,8 +1291,16 @@
           <t>2857485443-811-520115742569</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DEXTROSE 5% IN 0.225% SOD. CHLORIDE INF</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>DEXTROSE 5% IN 0.225% SOD. CHLORIDE INF detailed description.</t>
+        </is>
+      </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
@@ -1454,8 +1486,16 @@
           <t>5270845337-091-513634284308</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DEXTROSE 5% I.V INFUSION</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>DEXTROSE 5% I.V INFUSION detailed description.</t>
+        </is>
+      </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
@@ -1637,8 +1677,16 @@
           <t>8400924146-044-179230144264</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DEXTROSE 5% + 0.9% SODIUM CHLORIDE INFUSION</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>DEXTROSE 5% + 0.9% SODIUM CHLORIDE INFUSION detailed description.</t>
+        </is>
+      </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
@@ -1828,8 +1876,16 @@
           <t>3169528679-034-551768444251</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DEXTROSE 5% + 0.9% SODIUM CHLORIDE INFUSION</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>DEXTROSE 5% + 0.9% SODIUM CHLORIDE INFUSION detailed description.</t>
+        </is>
+      </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
@@ -2019,8 +2075,16 @@
           <t>5554215738-899-966343665343</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DEXTROSE 5% &amp; RINGER LACTATE INFUSION SOLUTION</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>DEXTROSE 5% &amp; RINGER LACTATE INFUSION SOLUTION detailed description.</t>
+        </is>
+      </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
@@ -2210,8 +2274,16 @@
           <t>9377267580-189-139599139148</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DEXTROSE 5%</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>DEXTROSE 5% detailed description.</t>
+        </is>
+      </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
@@ -2401,8 +2473,16 @@
           <t>1479001075-888-720258587315</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DEXTROSE 5%</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>DEXTROSE 5% detailed description.</t>
+        </is>
+      </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
@@ -2592,8 +2672,16 @@
           <t>1063613152-429-608068320275</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DEXTROSE 5%</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>DEXTROSE 5% detailed description.</t>
+        </is>
+      </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
@@ -2779,8 +2867,16 @@
           <t>5760253019-777-141910086304</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DEXTROSE 5% IN RINGER SOLUTION</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>DEXTROSE 5% IN RINGER SOLUTION detailed description.</t>
+        </is>
+      </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
@@ -2966,8 +3062,16 @@
           <t>8188163811-935-213478522262</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DEXTROSE 5% INFUSION</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>DEXTROSE 5% INFUSION detailed description.</t>
+        </is>
+      </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
@@ -3157,8 +3261,16 @@
           <t>0501573873-788-325768536210</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DEXTROSE 5%</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>DEXTROSE 5% detailed description.</t>
+        </is>
+      </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
@@ -3348,8 +3460,16 @@
           <t>5578523060-722-376044816087</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DEXTROSE 10%+N.SALINE INJ</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>DEXTROSE 10%+N.SALINE INJ detailed description.</t>
+        </is>
+      </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
@@ -3539,8 +3659,16 @@
           <t>1412615317-051-575019611451</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DEXTROSE 5%</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>DEXTROSE 5% detailed description.</t>
+        </is>
+      </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
@@ -3726,8 +3854,16 @@
           <t>7069953542-363-205578247446</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DEXTROSE 5%</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>DEXTROSE 5% detailed description.</t>
+        </is>
+      </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
@@ -3909,8 +4045,16 @@
           <t>6743833557-823-647904835973</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DEXTROSE 40%</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>DEXTROSE 40% detailed description.</t>
+        </is>
+      </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
@@ -4096,8 +4240,16 @@
           <t>5717924974-445-791587796479</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DEXTROSE 4.3%IN 0.18%SOD.CHLORIDE INFU</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>DEXTROSE 4.3%IN 0.18%SOD.CHLORIDE INFU detailed description.</t>
+        </is>
+      </c>
       <c r="I20" t="n">
         <v>0</v>
       </c>
@@ -4291,8 +4443,16 @@
           <t>3477616147-740-018897524674</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DEXTROSE 4.3%IN 0.18%SOD.CHLORIDE INFU</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>DEXTROSE 4.3%IN 0.18%SOD.CHLORIDE INFU detailed description.</t>
+        </is>
+      </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
@@ -4482,8 +4642,16 @@
           <t>0868763791-733-067641793358</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DEXTROSE 25% INJ</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>DEXTROSE 25% INJ detailed description.</t>
+        </is>
+      </c>
       <c r="I22" t="n">
         <v>0</v>
       </c>
@@ -4669,8 +4837,16 @@
           <t>4849827695-817-825735868757</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DEXTROSE 25% INJ</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>DEXTROSE 25% INJ detailed description.</t>
+        </is>
+      </c>
       <c r="I23" t="n">
         <v>0</v>
       </c>
@@ -4856,8 +5032,16 @@
           <t>3903982313-469-584908490052</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DEXTROSE 25% INJ</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>DEXTROSE 25% INJ detailed description.</t>
+        </is>
+      </c>
       <c r="I24" t="n">
         <v>0</v>
       </c>
@@ -5039,8 +5223,16 @@
           <t>9132839466-236-523097115898</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DEXTROSE 25% INJ</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>DEXTROSE 25% INJ detailed description.</t>
+        </is>
+      </c>
       <c r="I25" t="n">
         <v>0</v>
       </c>
@@ -5230,8 +5422,16 @@
           <t>7328256519-698-156264072366</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DEXTROSE 25% INJ</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>DEXTROSE 25% INJ detailed description.</t>
+        </is>
+      </c>
       <c r="I26" t="n">
         <v>0</v>
       </c>
@@ -5421,8 +5621,16 @@
           <t>6348362059-585-808595417586</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DEXTROSE 20% W-V INFUSION</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>DEXTROSE 20% W-V INFUSION detailed description.</t>
+        </is>
+      </c>
       <c r="I27" t="n">
         <v>0</v>
       </c>
@@ -5608,8 +5816,16 @@
           <t>8351749644-747-480327534131</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DEXTROSE 20% W-V INFUSION</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>DEXTROSE 20% W-V INFUSION detailed description.</t>
+        </is>
+      </c>
       <c r="I28" t="n">
         <v>0</v>
       </c>
@@ -5791,8 +6007,16 @@
           <t>6857981308-165-348494181007</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DEXTROSE 20% INJ</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>DEXTROSE 20% INJ detailed description.</t>
+        </is>
+      </c>
       <c r="I29" t="n">
         <v>0</v>
       </c>
@@ -5982,8 +6206,16 @@
           <t>3969000417-560-033804190155</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DEXTROSE 20% INJ</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>DEXTROSE 20% INJ detailed description.</t>
+        </is>
+      </c>
       <c r="I30" t="n">
         <v>0</v>
       </c>
@@ -6173,8 +6405,16 @@
           <t>9462397220-820-732148347056</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ 20%W/V DEXTROSE injection, USP</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>20%W/V DEXTROSE injection, USP detailed description.</t>
+        </is>
+      </c>
       <c r="I31" t="n">
         <v>0</v>
       </c>
@@ -6360,8 +6600,16 @@
           <t>0290761964-474-730138636093</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DEXTROSE 20%</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>DEXTROSE 20% detailed description.</t>
+        </is>
+      </c>
       <c r="I32" t="n">
         <v>0</v>
       </c>
@@ -6551,8 +6799,16 @@
           <t>2924483331-404-605696631227</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DEXTROSE 2.5% IN 1-2 NORMAL SALINE</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>DEXTROSE 2.5% IN 1-2 NORMAL SALINE detailed description.</t>
+        </is>
+      </c>
       <c r="I33" t="n">
         <v>0</v>
       </c>
@@ -6742,8 +6998,16 @@
           <t>4945947566-264-163880565327</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DEXTROSE 40% INFUSION</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>DEXTROSE 40% INFUSION detailed description.</t>
+        </is>
+      </c>
       <c r="I34" t="n">
         <v>0</v>
       </c>
@@ -6929,8 +7193,16 @@
           <t>1090982361-366-659244077852</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DEXTROSE 40% INFUSION</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>DEXTROSE 40% INFUSION detailed description.</t>
+        </is>
+      </c>
       <c r="I35" t="n">
         <v>0</v>
       </c>
@@ -7116,8 +7388,16 @@
           <t>4928976500-512-952986423811</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DEXTROSE 40% INFUSION</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>DEXTROSE 40% INFUSION detailed description.</t>
+        </is>
+      </c>
       <c r="I36" t="n">
         <v>0</v>
       </c>
@@ -7299,8 +7579,16 @@
           <t>7693843516-543-884284502451</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DEXTROSE 40% INFUSION</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>DEXTROSE 40% INFUSION detailed description.</t>
+        </is>
+      </c>
       <c r="I37" t="n">
         <v>0</v>
       </c>
@@ -7486,8 +7774,16 @@
           <t>8814356499-531-895053895266</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DEXTROSE 5%</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>DEXTROSE 5% detailed description.</t>
+        </is>
+      </c>
       <c r="I38" t="n">
         <v>0</v>
       </c>
@@ -7669,8 +7965,16 @@
           <t>2215222722-561-813525069672</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DEXTROSE 5%</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>DEXTROSE 5% detailed description.</t>
+        </is>
+      </c>
       <c r="I39" t="n">
         <v>0</v>
       </c>
@@ -7860,8 +8164,16 @@
           <t>4065125293-797-046287141992</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DEXTROSE 5%</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>DEXTROSE 5% detailed description.</t>
+        </is>
+      </c>
       <c r="I40" t="n">
         <v>0</v>
       </c>
@@ -8043,8 +8355,16 @@
           <t>9610465579-059-546375356680</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DEXTROSE 5%</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>DEXTROSE 5% detailed description.</t>
+        </is>
+      </c>
       <c r="I41" t="n">
         <v>0</v>
       </c>
@@ -8234,8 +8554,16 @@
           <t>0243623183-551-276162013271</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DEXTROSE 5%</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>DEXTROSE 5% detailed description.</t>
+        </is>
+      </c>
       <c r="I42" t="n">
         <v>0</v>
       </c>
@@ -8425,8 +8753,16 @@
           <t>9436000701-584-705015348961</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DEXTROSE 5%</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>DEXTROSE 5% detailed description.</t>
+        </is>
+      </c>
       <c r="I43" t="n">
         <v>0</v>
       </c>
@@ -8803,8 +9139,16 @@
           <t>7260445191-772-341450919938</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DEXTROSE 5%</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>DEXTROSE 5% detailed description.</t>
+        </is>
+      </c>
       <c r="I45" t="n">
         <v>0</v>
       </c>
@@ -8990,8 +9334,16 @@
           <t>3999313517-416-641544236960</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DEXTROSE 5%</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>DEXTROSE 5% detailed description.</t>
+        </is>
+      </c>
       <c r="I46" t="n">
         <v>0</v>
       </c>
@@ -9181,8 +9533,16 @@
           <t>7671344666-999-540393329334</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DEXTROSE 5%</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>DEXTROSE 5% detailed description.</t>
+        </is>
+      </c>
       <c r="I47" t="n">
         <v>0</v>
       </c>
@@ -9372,8 +9732,16 @@
           <t>7433339880-182-468803216226</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DEXTROSE 5%</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>DEXTROSE 5% detailed description.</t>
+        </is>
+      </c>
       <c r="I48" t="n">
         <v>0</v>
       </c>
@@ -9563,8 +9931,16 @@
           <t>0006303834-431-278793870365</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DEXTROSE 5%</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>DEXTROSE 5% detailed description.</t>
+        </is>
+      </c>
       <c r="I49" t="n">
         <v>0</v>
       </c>
@@ -9750,8 +10126,16 @@
           <t>7270877976-738-489110585656</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DEXTROSE 5%</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>DEXTROSE 5% detailed description.</t>
+        </is>
+      </c>
       <c r="I50" t="n">
         <v>0</v>
       </c>
@@ -9941,8 +10325,16 @@
           <t>5104209967-778-647439450231</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ 40% w/v DEXTROSE Injection USP</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>40% w/v DEXTROSE Injection USP detailed description.</t>
+        </is>
+      </c>
       <c r="I51" t="n">
         <v>0</v>
       </c>
@@ -10128,8 +10520,16 @@
           <t>4414300617-590-068592230866</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DEXTROSE 5%</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>DEXTROSE 5% detailed description.</t>
+        </is>
+      </c>
       <c r="I52" t="n">
         <v>0</v>
       </c>
@@ -11885,8 +12285,16 @@
           <t>9353265611-794-383807198091</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DAKTARIN POWDER 2%</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>DAKTARIN POWDER 2% detailed description.</t>
+        </is>
+      </c>
       <c r="I61" t="n">
         <v>0</v>
       </c>
@@ -12267,8 +12675,16 @@
           <t>8965492532-222-379783364447</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr"/>
-      <c r="H63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DAROXIME 250 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>DAROXIME 250 mg film-coated tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I63" t="n">
         <v>0</v>
       </c>
@@ -12840,8 +13256,16 @@
           <t>9368171598-678-476700995429</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr"/>
-      <c r="H66" t="inlineStr"/>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DAONIL M 250/1.25MG TABLETS</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>DAONIL M 250/1.25MG TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I66" t="n">
         <v>0</v>
       </c>
@@ -13813,8 +14237,16 @@
           <t>8476448719-873-712814268612</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr"/>
-      <c r="H71" t="inlineStr"/>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CURACNE 20MG SOFT GELATIN CAPSULE</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>CURACNE 20MG SOFT GELATIN CAPSULE detailed description.</t>
+        </is>
+      </c>
       <c r="I71" t="n">
         <v>0</v>
       </c>
@@ -14000,8 +14432,16 @@
           <t>2382093277-962-785994215288</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr"/>
-      <c r="H72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CURACNE 10MG SOFT GELATIN CAPSULE</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>CURACNE 10MG SOFT GELATIN CAPSULE detailed description.</t>
+        </is>
+      </c>
       <c r="I72" t="n">
         <v>0</v>
       </c>
@@ -14390,8 +14830,16 @@
           <t>7522319902-049-983044753452</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr"/>
-      <c r="H74" t="inlineStr"/>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CROTAPHIL 10% LOTION</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>CROTAPHIL 10% LOTION detailed description.</t>
+        </is>
+      </c>
       <c r="I74" t="n">
         <v>0</v>
       </c>
@@ -14581,8 +15029,16 @@
           <t>7490119800-402-335319985686</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr"/>
-      <c r="H75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CROTAPHIL 10% CREAM</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>CROTAPHIL 10% CREAM detailed description.</t>
+        </is>
+      </c>
       <c r="I75" t="n">
         <v>0</v>
       </c>
@@ -16340,8 +16796,16 @@
           <t>7188105867-486-146682126933</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr"/>
-      <c r="H84" t="inlineStr"/>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CURAM 156.25MG-5ML POWDER FOR SUSP</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>CURAM 156.25MG-5ML POWDER FOR SUSP detailed description.</t>
+        </is>
+      </c>
       <c r="I84" t="n">
         <v>0</v>
       </c>
@@ -16933,8 +17397,16 @@
           <t>1421082190-168-006208248747</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr"/>
-      <c r="H87" t="inlineStr"/>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ C-VITAL 1G EFFERVESCENT TABLETS SUGAR FREE</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>C-VITAL 1G EFFERVESCENT TABLETS SUGAR FREE detailed description.</t>
+        </is>
+      </c>
       <c r="I87" t="n">
         <v>0</v>
       </c>
@@ -17120,8 +17592,16 @@
           <t>6902716900-747-601294517316</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr"/>
-      <c r="H88" t="inlineStr"/>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CUTIVATE 0.005% ointment</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>CUTIVATE 0.005% ointment detailed description.</t>
+        </is>
+      </c>
       <c r="I88" t="n">
         <v>0</v>
       </c>
@@ -17510,8 +17990,16 @@
           <t>1251475278-292-929764131238</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr"/>
-      <c r="H90" t="inlineStr"/>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CURAM 457MG-5ML POW. FOR ORAL SUSPENSION</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>CURAM 457MG-5ML POW. FOR ORAL SUSPENSION detailed description.</t>
+        </is>
+      </c>
       <c r="I90" t="n">
         <v>0</v>
       </c>
@@ -17701,8 +18189,16 @@
           <t>2429589350-234-706451198726</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr"/>
-      <c r="H91" t="inlineStr"/>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CUTIVATE 0.05% cream</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>CUTIVATE 0.05% cream detailed description.</t>
+        </is>
+      </c>
       <c r="I91" t="n">
         <v>0</v>
       </c>
@@ -17888,8 +18384,16 @@
           <t>3975195176-042-361498002767</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr"/>
-      <c r="H92" t="inlineStr"/>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DERMOFUCIN 2% OINTMENT</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>DERMOFUCIN 2% OINTMENT detailed description.</t>
+        </is>
+      </c>
       <c r="I92" t="n">
         <v>0</v>
       </c>
@@ -18278,8 +18782,16 @@
           <t>6368485891-601-564703564020</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr"/>
-      <c r="H94" t="inlineStr"/>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DERMOFIX 2% CREAM</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>DERMOFIX 2% CREAM detailed description.</t>
+        </is>
+      </c>
       <c r="I94" t="n">
         <v>0</v>
       </c>
@@ -18465,8 +18977,16 @@
           <t>1046805764-927-835899530153</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr"/>
-      <c r="H95" t="inlineStr"/>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DERMOCORT CREAM</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>DERMOCORT CREAM detailed description.</t>
+        </is>
+      </c>
       <c r="I95" t="n">
         <v>0</v>
       </c>
@@ -18839,8 +19359,16 @@
           <t>3969425125-395-512758549581</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr"/>
-      <c r="H97" t="inlineStr"/>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DERMATIN CREAM 1%</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>DERMATIN CREAM 1% detailed description.</t>
+        </is>
+      </c>
       <c r="I97" t="n">
         <v>0</v>
       </c>
@@ -19229,8 +19757,16 @@
           <t>3535991300-315-238868260781</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr"/>
-      <c r="H99" t="inlineStr"/>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DERMAMED 0.05% OINTMENT</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>DERMAMED 0.05% OINTMENT detailed description.</t>
+        </is>
+      </c>
       <c r="I99" t="n">
         <v>0</v>
       </c>

--- a/product_upload/packages/15/file.xlsx
+++ b/product_upload/packages/15/file.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>Manufacturer Name</t>
+          <t>Manufacturer</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
@@ -20378,7 +20378,7 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Manufacturer Name</t>
+          <t>Manufacturer</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
@@ -22137,7 +22137,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W21"/>
+  <dimension ref="A1:X21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22218,40 +22218,45 @@
       </c>
       <c r="P1" t="inlineStr">
         <is>
+          <t>Size unit</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
           <t>Manufacturer *</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Period After Opening.1</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Usage Instructions</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Warnings</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>Manufacturer Name</t>
-        </is>
-      </c>
       <c r="V1" t="inlineStr">
         <is>
+          <t>Manufacturer</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>Ingredients</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Seller SKU</t>
         </is>
@@ -22331,38 +22336,43 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>44.54</v>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>SKU-9F0B489DF7CC</t>
         </is>
@@ -22442,38 +22452,43 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>462.84</v>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>SKU-84C48657A165</t>
         </is>
@@ -22553,38 +22568,43 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>56.63</v>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>SKU-091651EA21BE</t>
         </is>
@@ -22664,38 +22684,43 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>51.57</v>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>SKU-7348A57795DE</t>
         </is>
@@ -22775,38 +22800,43 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>32.23</v>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>SKU-FBE99303C427</t>
         </is>
@@ -22886,38 +22916,43 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>448.37</v>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>SKU-B3E73661A217</t>
         </is>
@@ -22997,38 +23032,43 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>255.22</v>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>SKU-88453BC061E7</t>
         </is>
@@ -23108,38 +23148,43 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>385.7</v>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>SKU-A3F87921111E</t>
         </is>
@@ -23219,38 +23264,43 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>262.6</v>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="X10" t="inlineStr">
         <is>
           <t>SKU-3CDB8300509A</t>
         </is>
@@ -23330,38 +23380,43 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
         <v>447.11</v>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="X11" t="inlineStr">
         <is>
           <t>SKU-8A85C717FFC7</t>
         </is>
@@ -23441,38 +23496,43 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>301.42</v>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
+      <c r="X12" t="inlineStr">
         <is>
           <t>SKU-81ABEA1344B7</t>
         </is>
@@ -23552,38 +23612,43 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q13" t="n">
+      <c r="R13" t="n">
         <v>396.7</v>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
+      <c r="X13" t="inlineStr">
         <is>
           <t>SKU-0921B8871FEF</t>
         </is>
@@ -23663,38 +23728,43 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q14" t="n">
+      <c r="R14" t="n">
         <v>404.65</v>
       </c>
-      <c r="R14" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
+      <c r="X14" t="inlineStr">
         <is>
           <t>SKU-DAA2A726F88E</t>
         </is>
@@ -23774,38 +23844,43 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q15" t="n">
+      <c r="R15" t="n">
         <v>494.45</v>
       </c>
-      <c r="R15" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
+      <c r="X15" t="inlineStr">
         <is>
           <t>SKU-0427C106C43D</t>
         </is>
@@ -23885,38 +23960,43 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q16" t="n">
+      <c r="R16" t="n">
         <v>72.52</v>
       </c>
-      <c r="R16" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
+      <c r="X16" t="inlineStr">
         <is>
           <t>SKU-040E51D202AC</t>
         </is>
@@ -23996,38 +24076,43 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q17" t="n">
+      <c r="R17" t="n">
         <v>341.74</v>
       </c>
-      <c r="R17" t="inlineStr">
+      <c r="S17" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
+      <c r="T17" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr">
+      <c r="U17" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr">
+      <c r="V17" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
+      <c r="X17" t="inlineStr">
         <is>
           <t>SKU-AE3B9F5DA6AE</t>
         </is>
@@ -24107,38 +24192,43 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q18" t="n">
+      <c r="R18" t="n">
         <v>476.44</v>
       </c>
-      <c r="R18" t="inlineStr">
+      <c r="S18" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
+      <c r="T18" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr">
+      <c r="U18" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr">
+      <c r="V18" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
+      <c r="X18" t="inlineStr">
         <is>
           <t>SKU-3E23EDE5D020</t>
         </is>
@@ -24218,38 +24308,43 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q19" t="n">
+      <c r="R19" t="n">
         <v>311.93</v>
       </c>
-      <c r="R19" t="inlineStr">
+      <c r="S19" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="T19" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr">
+      <c r="U19" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U19" t="inlineStr">
+      <c r="V19" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
+      <c r="X19" t="inlineStr">
         <is>
           <t>SKU-34E3D0AB0069</t>
         </is>
@@ -24329,38 +24424,43 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q20" t="n">
+      <c r="R20" t="n">
         <v>164.14</v>
       </c>
-      <c r="R20" t="inlineStr">
+      <c r="S20" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="T20" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr">
+      <c r="U20" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr">
+      <c r="V20" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W20" t="inlineStr">
+      <c r="X20" t="inlineStr">
         <is>
           <t>SKU-9C169E05E23F</t>
         </is>
@@ -24440,38 +24540,43 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q21" t="n">
+      <c r="R21" t="n">
         <v>49.87</v>
       </c>
-      <c r="R21" t="inlineStr">
+      <c r="S21" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="T21" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr">
+      <c r="U21" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr">
+      <c r="V21" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W21" t="inlineStr">
+      <c r="X21" t="inlineStr">
         <is>
           <t>SKU-A33626DD6EE7</t>
         </is>
